--- a/Diarias/Diarias.xlsx
+++ b/Diarias/Diarias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A552505-B268-4D24-B120-F78AC682DA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F09BCB-E42D-4C53-BA82-B638A2643D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{202230F5-B999-493F-8126-8B87BE85ADD7}"/>
   </bookViews>
@@ -551,7 +551,9 @@
       <c r="E3" s="1">
         <v>9.3885126271552579</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1">
+        <v>11.183411357530629</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>

--- a/Diarias/Diarias.xlsx
+++ b/Diarias/Diarias.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F09BCB-E42D-4C53-BA82-B638A2643D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE07A55B-4ED3-4336-ACF4-72DC0742B59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{202230F5-B999-493F-8126-8B87BE85ADD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +62,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1E293B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -107,13 +113,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,7 +561,9 @@
       <c r="F3" s="1">
         <v>11.183411357530629</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1">
+        <v>15.742341042778605</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -593,7 +602,7 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>

--- a/Diarias/Diarias.xlsx
+++ b/Diarias/Diarias.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE07A55B-4ED3-4336-ACF4-72DC0742B59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F181AAAF-1A4D-452F-8CAC-DFD498E1D090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{202230F5-B999-493F-8126-8B87BE85ADD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +62,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1E293B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -121,6 +127,7 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,7 +569,7 @@
         <v>11.183411357530629</v>
       </c>
       <c r="G3" s="1">
-        <v>15.742341042778605</v>
+        <v>15.786909970989406</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -573,6 +580,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C4" s="3"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
